--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_38.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_38.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>16</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
         <v>11</v>
@@ -668,17 +668,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -734,13 +734,13 @@
         <v>16</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -762,7 +762,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -830,13 +830,13 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
         <v>11</v>
@@ -866,12 +866,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -932,10 +932,10 @@
         <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
         <v>17</v>
@@ -960,42 +960,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_32.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_11.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_47.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="n">
         <v>3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1127,10 +1127,10 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V7" t="n">
         <v>10</v>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1226,10 +1226,10 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
         <v>16</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1325,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
         <v>10</v>
@@ -1334,7 +1334,7 @@
         <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_47.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_11.jpg</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1427,13 +1427,13 @@
         <v>10</v>
       </c>
       <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" t="n">
         <v>9</v>
       </c>
-      <c r="V10" t="n">
-        <v>4</v>
-      </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1523,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
         <v>11</v>
@@ -1554,42 +1554,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_31.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_17.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_11.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_21.jpg</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W12" t="n">
         <v>6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
@@ -1730,7 +1730,7 @@
         <v>16</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>11</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
         <v>17</v>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2021,10 +2021,10 @@
         <v>15</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
         <v>12</v>
@@ -2049,17 +2049,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2117,13 +2117,13 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
         <v>17</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2216,16 +2216,16 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2315,13 +2315,13 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U19" t="n">
         <v>10</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
         <v>12</v>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2417,10 +2417,10 @@
         <v>10</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
         <v>5</v>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2460,17 +2460,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
         <v>18</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -2544,42 +2544,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_02.jpg</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_09.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_46.jpg</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_02.jpg</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2612,16 +2612,16 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
         <v>8</v>
       </c>
-      <c r="U22" t="n">
-        <v>6</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>9</v>
-      </c>
-      <c r="W22" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -2643,42 +2643,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_17.jpg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_02.jpg</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
+        <v>8</v>
+      </c>
+      <c r="V23" t="n">
         <v>9</v>
       </c>
-      <c r="V23" t="n">
-        <v>4</v>
-      </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2810,7 +2810,7 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24" t="n">
         <v>5</v>
@@ -2819,7 +2819,7 @@
         <v>15</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2912,10 +2912,10 @@
         <v>5</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
         <v>10</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
         <v>12</v>
@@ -3017,7 +3017,7 @@
         <v>18</v>
       </c>
       <c r="W26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -3242,17 +3242,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3262,17 +3262,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3308,13 +3308,13 @@
         <v>16</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3346,17 +3346,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_32.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3404,16 +3404,16 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
         <v>5</v>
       </c>
       <c r="V30" t="n">
+        <v>6</v>
+      </c>
+      <c r="W30" t="n">
         <v>3</v>
-      </c>
-      <c r="W30" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3506,10 +3506,10 @@
         <v>5</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W31" t="n">
         <v>12</v>
@@ -3534,42 +3534,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_32.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_41.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_21.jpg</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_41.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_32.jpg</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
         <v>10</v>
       </c>
       <c r="W32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3648,17 +3648,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3701,16 +3701,16 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V33" t="n">
         <v>12</v>
       </c>
       <c r="W33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3800,10 +3800,10 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
         <v>17</v>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3899,7 +3899,7 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
         <v>10</v>
@@ -3908,7 +3908,7 @@
         <v>16</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4001,10 +4001,10 @@
         <v>10</v>
       </c>
       <c r="U36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
         <v>11</v>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
         <v>16</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4196,10 +4196,10 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V38" t="n">
         <v>12</v>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4295,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
         <v>17</v>
@@ -4304,7 +4304,7 @@
         <v>5</v>
       </c>
       <c r="W39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4400,10 +4400,10 @@
         <v>11</v>
       </c>
       <c r="V40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -4529,19 +4529,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_38.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_43.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_02.jpg</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>key</t>
@@ -4549,17 +4549,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4595,13 +4595,13 @@
         <v>15</v>
       </c>
       <c r="U42" t="n">
+        <v>3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>9</v>
+      </c>
+      <c r="W42" t="n">
         <v>7</v>
-      </c>
-      <c r="V42" t="n">
-        <v>4</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -4623,17 +4623,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4643,17 +4643,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4691,13 +4691,13 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
         <v>12</v>
@@ -4722,19 +4722,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>stimuli/house/house_43.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_17.jpg</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_07.jpg</t>
@@ -4742,17 +4742,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4790,13 +4790,13 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U44" t="n">
+        <v>9</v>
+      </c>
+      <c r="V44" t="n">
         <v>4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>8</v>
       </c>
       <c r="W44" t="n">
         <v>17</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4889,7 +4889,7 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U45" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
         <v>18</v>
       </c>
       <c r="W45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4945,17 +4945,17 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4991,13 +4991,13 @@
         <v>10</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5039,17 +5039,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5087,13 +5087,13 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W47" t="n">
         <v>15</v>
@@ -5118,19 +5118,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_09.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_38.jpg</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>stimuli/jacket/jacket_49.jpg</t>
@@ -5138,17 +5138,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5186,13 +5186,13 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
         <v>6</v>
-      </c>
-      <c r="V48" t="n">
-        <v>3</v>
       </c>
       <c r="W48" t="n">
         <v>10</v>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5232,17 +5232,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V49" t="n">
         <v>18</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5384,13 +5384,13 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U50" t="n">
         <v>5</v>
       </c>
       <c r="V50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W50" t="n">
         <v>17</v>
@@ -5420,19 +5420,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_46.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_07.jpg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_07.jpg</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_09.jpg</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>dog</t>
@@ -5440,17 +5440,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5486,13 +5486,13 @@
         <v>5</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V51" t="n">
         <v>17</v>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U52" t="n">
         <v>12</v>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5690,7 +5690,7 @@
         <v>15</v>
       </c>
       <c r="W53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>16</v>
       </c>
       <c r="V54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W54" t="n">
         <v>11</v>
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5836,17 +5836,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5882,13 +5882,13 @@
         <v>16</v>
       </c>
       <c r="U55" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5978,13 +5978,13 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U56" t="n">
         <v>5</v>
       </c>
       <c r="V56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6080,10 +6080,10 @@
         <v>5</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W57" t="n">
         <v>11</v>
@@ -6108,42 +6108,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_32.jpg</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_11.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_21.jpg</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_47.jpg</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_32.jpg</t>
-        </is>
-      </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6176,16 +6176,16 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6</v>
+      </c>
+      <c r="V58" t="n">
+        <v>4</v>
+      </c>
+      <c r="W58" t="n">
         <v>1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>3</v>
-      </c>
-      <c r="V58" t="n">
-        <v>8</v>
-      </c>
-      <c r="W58" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6275,10 +6275,10 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V59" t="n">
         <v>10</v>
@@ -6306,17 +6306,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6326,17 +6326,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6374,13 +6374,13 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V60" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W60" t="n">
         <v>16</v>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6415,17 +6415,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6473,16 +6473,16 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U61" t="n">
         <v>10</v>
       </c>
       <c r="V61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="U62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V62" t="n">
         <v>16</v>
       </c>
       <c r="W62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6618,17 +6618,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V63" t="n">
         <v>12</v>
       </c>
       <c r="W63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -6702,42 +6702,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_21.jpg</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_31.jpg</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_21.jpg</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_32.jpg</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_21.jpg</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,16 +6770,16 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U64" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V64" t="n">
         <v>5</v>
       </c>
       <c r="W64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6869,7 +6869,7 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U65" t="n">
         <v>17</v>
@@ -6878,7 +6878,7 @@
         <v>12</v>
       </c>
       <c r="W65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>15</v>
       </c>
       <c r="V67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" t="n">
         <v>17</v>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7169,10 +7169,10 @@
         <v>15</v>
       </c>
       <c r="U68" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W68" t="n">
         <v>12</v>
@@ -7197,42 +7197,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_38.jpg</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_46.jpg</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_09.jpg</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_38.jpg</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_46.jpg</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
-        </is>
-      </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7265,16 +7265,16 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>6</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>7</v>
-      </c>
-      <c r="U69" t="n">
-        <v>3</v>
-      </c>
-      <c r="V69" t="n">
-        <v>6</v>
-      </c>
-      <c r="W69" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7364,10 +7364,10 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U70" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V70" t="n">
         <v>5</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7463,13 +7463,13 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U71" t="n">
         <v>10</v>
       </c>
       <c r="V71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W71" t="n">
         <v>17</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7565,13 +7565,13 @@
         <v>10</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72" t="n">
         <v>18</v>
       </c>
       <c r="W72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -7593,19 +7593,19 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_02.jpg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_43.jpg</t>
-        </is>
-      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>stimuli/key/key_25.jpg</t>
@@ -7613,17 +7613,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7661,13 +7661,13 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U73" t="n">
+        <v>4</v>
+      </c>
+      <c r="V73" t="n">
         <v>8</v>
-      </c>
-      <c r="V73" t="n">
-        <v>9</v>
       </c>
       <c r="W73" t="n">
         <v>15</v>
@@ -7692,12 +7692,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7707,17 +7707,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7760,16 +7760,16 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U74" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V74" t="n">
         <v>12</v>
       </c>
       <c r="W74" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7806,17 +7806,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V75" t="n">
         <v>5</v>
       </c>
       <c r="W75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7958,13 +7958,13 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U76" t="n">
         <v>5</v>
       </c>
       <c r="V76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W76" t="n">
         <v>10</v>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8060,13 +8060,13 @@
         <v>5</v>
       </c>
       <c r="U77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V77" t="n">
         <v>18</v>
       </c>
       <c r="W77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8156,7 +8156,7 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U78" t="n">
         <v>12</v>
@@ -8165,7 +8165,7 @@
         <v>15</v>
       </c>
       <c r="W78" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>17</v>
       </c>
       <c r="V79" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W79" t="n">
         <v>18</v>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8360,7 +8360,7 @@
         <v>16</v>
       </c>
       <c r="V80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W80" t="n">
         <v>17</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8456,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="U81" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V81" t="n">
         <v>5</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_11.jpg</t>
+          <t>stimuli/house/house_17.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8552,13 +8552,13 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U82" t="n">
         <v>5</v>
       </c>
       <c r="V82" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W82" t="n">
         <v>17</v>
@@ -8588,19 +8588,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_41.jpg</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_41.jpg</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_32.jpg</t>
-        </is>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>dog</t>
@@ -8608,17 +8608,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8654,13 +8654,13 @@
         <v>5</v>
       </c>
       <c r="U83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V83" t="n">
         <v>10</v>
       </c>
       <c r="W83" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -8682,17 +8682,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_31.jpg</t>
+          <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8702,17 +8702,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8750,13 +8750,13 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W84" t="n">
         <v>12</v>
@@ -8781,17 +8781,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8849,13 +8849,13 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U85" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V85" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W85" t="n">
         <v>17</v>
@@ -8880,42 +8880,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_10.jpg</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_11.jpg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_17.jpg</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_05.jpg</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_47.jpg</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_11.jpg</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_31.jpg</t>
-        </is>
-      </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8948,16 +8948,16 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
+        <v>7</v>
+      </c>
+      <c r="U86" t="n">
+        <v>4</v>
+      </c>
+      <c r="V86" t="n">
+        <v>9</v>
+      </c>
+      <c r="W86" t="n">
         <v>2</v>
-      </c>
-      <c r="U86" t="n">
-        <v>8</v>
-      </c>
-      <c r="V86" t="n">
-        <v>4</v>
-      </c>
-      <c r="W86" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9047,13 +9047,13 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U87" t="n">
         <v>10</v>
       </c>
       <c r="V87" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W87" t="n">
         <v>16</v>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9149,13 +9149,13 @@
         <v>10</v>
       </c>
       <c r="U88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V88" t="n">
         <v>16</v>
       </c>
       <c r="W88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hand/hand_47.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_21.jpg</t>
+          <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V89" t="n">
         <v>11</v>
       </c>
       <c r="W89" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_10.jpg</t>
+          <t>stimuli/bread/bread_21.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_32.jpg</t>
+          <t>stimuli/ball/ball_31.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_47.jpg</t>
+          <t>stimuli/chair/chair_11.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9344,16 +9344,16 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V90" t="n">
         <v>16</v>
       </c>
       <c r="W90" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -9375,42 +9375,42 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_31.jpg</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_31.jpg</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_17.jpg</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_32.jpg</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_31.jpg</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_11.jpg</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_21.jpg</t>
-        </is>
-      </c>
       <c r="I91" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9443,16 +9443,16 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U91" t="n">
         <v>17</v>
       </c>
       <c r="V91" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_05.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9548,7 +9548,7 @@
         <v>11</v>
       </c>
       <c r="V92" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W92" t="n">
         <v>12</v>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9647,7 +9647,7 @@
         <v>15</v>
       </c>
       <c r="V93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W93" t="n">
         <v>12</v>
@@ -9677,14 +9677,14 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_38.jpg</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
-        </is>
-      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_07.jpg</t>
@@ -9697,12 +9697,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9743,10 +9743,10 @@
         <v>15</v>
       </c>
       <c r="U94" t="n">
+        <v>3</v>
+      </c>
+      <c r="V94" t="n">
         <v>7</v>
-      </c>
-      <c r="V94" t="n">
-        <v>2</v>
       </c>
       <c r="W94" t="n">
         <v>17</v>
@@ -9771,42 +9771,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_38.jpg</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_46.jpg</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_38.jpg</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_09.jpg</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9839,16 +9839,16 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
+        <v>3</v>
+      </c>
+      <c r="U95" t="n">
+        <v>6</v>
+      </c>
+      <c r="V95" t="n">
+        <v>2</v>
+      </c>
+      <c r="W95" t="n">
         <v>7</v>
-      </c>
-      <c r="U95" t="n">
-        <v>3</v>
-      </c>
-      <c r="V95" t="n">
-        <v>1</v>
-      </c>
-      <c r="W95" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -9870,17 +9870,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/flower/flower_46.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9890,17 +9890,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9938,13 +9938,13 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U96" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W96" t="n">
         <v>17</v>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -9979,17 +9979,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10037,16 +10037,16 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U97" t="n">
         <v>10</v>
       </c>
       <c r="V97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W97" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10139,10 +10139,10 @@
         <v>10</v>
       </c>
       <c r="U98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V98" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W98" t="n">
         <v>17</v>
@@ -10167,17 +10167,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10187,17 +10187,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10235,13 +10235,13 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U99" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V99" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W99" t="n">
         <v>15</v>
@@ -10266,12 +10266,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/chair/chair_02.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10281,17 +10281,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10334,16 +10334,16 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U100" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V100" t="n">
         <v>15</v>
       </c>
       <c r="W100" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10433,10 +10433,10 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V101" t="n">
         <v>5</v>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/house/house_43.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10532,7 +10532,7 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U102" t="n">
         <v>5</v>
@@ -10541,7 +10541,7 @@
         <v>18</v>
       </c>
       <c r="W102" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_46.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10634,10 +10634,10 @@
         <v>5</v>
       </c>
       <c r="U103" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V103" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W103" t="n">
         <v>10</v>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/hammer/hammer_46.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_46.jpg</t>
+          <t>stimuli/ball/ball_09.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10730,7 +10730,7 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U104" t="n">
         <v>12</v>
@@ -10739,7 +10739,7 @@
         <v>15</v>
       </c>
       <c r="W104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_02.jpg</t>
+          <t>stimuli/house/house_43.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10835,7 +10835,7 @@
         <v>17</v>
       </c>
       <c r="V105" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W105" t="n">
         <v>18</v>
